--- a/docs/import-sample/取り込み用.xlsx
+++ b/docs/import-sample/取り込み用.xlsx
@@ -1673,24 +1673,24 @@
       <c r="D26" s="5" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:D500">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A500">
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
       <formula>AND($A2&lt;&gt;"",COUNTIF($A:$A,$A2)&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C500">
-    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>AND($C2&lt;&gt;"",COUNTIFS(INDIRECT("大会!$A:$A"),"チーム",INDIRECT("大会!$B:$B"),$C2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D500">
-    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
       <formula>AND($D2&lt;&gt;"",COUNTIFS(INDIRECT("大会!$A:$A"),"部",INDIRECT("大会!$B:$B"),$D2)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:D500">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
+      <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3224,50 +3224,36 @@
       <c r="M31" s="5" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:M500">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A500">
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
       <formula>AND($A2&lt;&gt;"",COUNTIFS(INDIRECT("大会!$A:$A"),"段",INDIRECT("大会!$B:$B"),$A2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F500">
-    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
       <formula>AND($F2&lt;&gt;"",COUNTIFS(INDIRECT("大会!$A:$A"),"部",INDIRECT("大会!$B:$B"),$F2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:E500">
-    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
       <formula>AND(D2&lt;&gt;"",COUNTIFS(INDIRECT("大会!$A:$A"),"チーム",INDIRECT("大会!$B:$B"),D2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H500">
-    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="1">
       <formula>AND($H2&lt;&gt;"",IFERROR($H2&gt;INDEX(INDIRECT("大会!$C:$C"),MATCH("面数",INDIRECT("大会!$A:$A"),0)),FALSE))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:M500">
-    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
       <formula>AND(J2&lt;&gt;"",COUNTIF(INDIRECT("選手!$A:$A"),J2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="数字" error="1 以上の整数を書いてください" type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="数字" error="1 以上の整数を書いてください" type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="数字" error="1 以上の整数を書いてください" type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="数字" error="1 以上の整数を書いてください" type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
-  </dataValidations>
+  <conditionalFormatting sqref="A2:M500">
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="0">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
